--- a/doc/zh_TW.xlsx
+++ b/doc/zh_TW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\workSpace\BMSTOOL\bmsTool\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8737AE0B-C55F-4F50-9639-CF0AB54FCC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{42F506AE-09DA-4AF8-B2B0-6A9BA8560330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1068EAC0-E899-4EA3-939C-1446E2C96548}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D38BF958-9624-4D8F-8E6F-985DB5F32475}"/>
   </bookViews>
   <sheets>
     <sheet name="zh_TW" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="281">
   <si>
     <t>單體電池低壓告警</t>
   </si>
@@ -526,6 +526,9 @@
     <t>更改後的值,U16,1,0,</t>
   </si>
   <si>
+    <t>{"evt_id":{"5358":"預充結束時間定值","5359":"預充結束電流定值","5360":"預留傳感器量程","5361":"簇電池額定Ah數","5362":"充放電電流死區閾值","5363":"簇電池充滿回差值","5364":"簇電池放空回差值","5365":"環控溫度回差值","5366":"環控溫度上限值","5367":"環控溫度下限值","5368":"簇電池SOC上限告警值","5369":"簇電池SOC下限值","5370":"簇極柱溫度越上限值","5371":"簇極柱高溫保護值","5372":"簇電池絕緣電阻告警值","5373":"簇電池漏電流告警值","5374":"單體壓差過高告警值","5375":"單體壓差過高保護值","5376":"單體電壓過高告警值","5377":"單體電壓過高保護值","5378":"單體電壓過低告警值","5379":"單體電壓過低保護值","5380":"單體溫度過高告警值","5381":"單體溫度過高保護值","5382":"單體溫度過低告警值","5383":"單體溫度過低保護值","5384":"單體溫差過高告警值","5385":"單體溫差過高保護值","5386":"單體溫升過高告警值","5387":"單體溫升過高保護值","5388":"Pack極柱溫度過高告警值","5389":"Pack極柱溫度過高保護值","5390":"充放電電流過負荷告警值","5391":"充放電電流過負荷保護值","5392":"短路電流保護值","5393":"簇電壓過高告警值","5394":"簇電壓過高保護值","5395":"簇電壓過低告警值","5396":"簇電壓過低保護值","5397":"簇電池絕緣電阻保護值","5398":"簇電池漏電流保護值","5399":"告警延時","5400":"保護延時","5401":"簇電池容量","5402":"簇電池校正容量","5403":"簇電池剩餘電量","5404":"充放電額定電流","5405":"電流傳感器量程","5406":"漏電流傳感器量程","5407":"電壓傳感器量程","5408":"電池均衡控制模式","5409":"均衡配置參數/閾值","5410":"均衡啓動電壓差值","5411":"簇電池單元數量","5412":"BMU單體電池個數","5413":"BMU模塊溫度個數","5414":"BMU極柱溫度個數","5415":"nBC報警屏蔽位","5416":"nBC故障屏蔽位","5417":"CMU功能使能位1","5418":"IP地址低位","5419":"IP地址高位 ","5420":"NTP服務器地址低位","5421":"NTP服務器地址高位","5422":"數據屏蔽位1","5423":"數據屏蔽位2","5424":"數據屏蔽位3","5425":"數據屏蔽位4","5426":"系統保護屏蔽寄存器1","5427":"系統保護屏蔽寄存器2","5428":"系統告警屏蔽寄存器1","5429":"系統告警屏蔽寄存器2","5430":"CMU功能使能位2","5431":"充滿放空簇電壓回差值","5432":"單體電壓數據屏蔽位","5433":"溫度數據屏蔽位"}}</t>
+  </si>
+  <si>
     <t>CMU升級檔校驗失敗</t>
   </si>
   <si>
@@ -757,11 +760,143 @@
     <t>跳變後溫度值,U16,0.1,0,℃</t>
   </si>
   <si>
-    <t>更改前的值,U16,1,0,</t>
+    <t>核容完成</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{"evt_id":{"5358":"預充結束時間定值","5359":"預充結束電流定值","5360":"預留傳感器量程","5361":"簇電池額定Ah數","5362":"充放電電流死區閾值","5363":"簇電池充滿回差值","5364":"簇電池放空回差值","5365":"環控溫度回差值","5366":"環控溫度上限值","5367":"環控溫度下限值","5368":"簇電池SOC上限告警值","5369":"簇電池SOC下限值","5370":"簇極柱溫度越上限值","5371":"簇極柱高溫保護值","5372":"簇電池絕緣電阻告警值","5373":"簇電池漏電流告警值","5374":"單體壓差過高告警值","5375":"單體壓差過高保護值","5376":"單體電壓過高告警值","5377":"單體電壓過高保護值","5378":"單體電壓過低告警值","5379":"單體電壓過低保護值","5380":"單體溫度過高告警值","5381":"單體溫度過高保護值","5382":"單體溫度過低告警值","5383":"單體溫度過低保護值","5384":"單體溫差過高告警值","5385":"單體溫差過高保護值","5386":"單體溫升過高告警值","5387":"單體溫升過高保護值","5388":"Pack極柱溫度過高告警值","5389":"Pack極柱溫度過高保護值","5390":"充放電電流過負荷告警值","5391":"充放電電流過負荷保護值","5392":"短路電流保護值","5393":"簇電壓過高告警值","5394":"簇電壓過高保護值","5395":"簇電壓過低告警值","5396":"簇電壓過低保護值","5397":"簇電池絕緣電阻保護值","5398":"簇電池漏電流保護值","5399":"告警延時","5400":"保護延時","5401":"簇電池容量","5402":"簇電池校正容量","5403":"簇電池剩餘電量","5404":"充放電額定電流","5405":"電流傳感器量程","5406":"漏電流傳感器量程","5407":"電壓傳感器量程","5408":"電池均衡控制模式","5409":"均衡配置參數/閾值","5410":"均衡啓動電壓差值","5411":"簇電池單元數量","5412":"BMU單體電池個數","5413":"BMU模塊溫度個數","5414":"BMU極柱溫度個數","5415":"nBC報警屏蔽位","5416":"nBC故障屏蔽位","5417":"CMU功能使能位1","5418":"IP地址低位","5419":"IP地址高位 ","5420":"NTP服務器地址低位","5421":"NTP服務器地址高位","5422":"數據屏蔽位1","5423":"數據屏蔽位2","5424":"數據屏蔽位3","5425":"數據屏蔽位4","5426":"系統保護屏蔽寄存器1","5427":"系統保護屏蔽寄存器2","5428":"系統告警屏蔽寄存器1","5429":"系統告警屏蔽寄存器2","5430":"CMU功能使能位2","5431":"充滿放空簇電壓回差值","5432":"單體電壓數據屏蔽位","5433":"溫度數據屏蔽位"}}</t>
+    <t>CMU-BMU通信故障</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CMU-INR通信故障</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簇极柱高温锁定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簇電壓差值預警</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簇電電壓差值,U16,0.0001,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>門限電壓,U16,0.0001,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>過壓自動跳閘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>過壓ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>電壓值,U16,0.0001,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>電壓過壓限值,U16,0.0001,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOH,U16,1,0,‰</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOH,U16,1,0,%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>電芯電壓異常</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>異常BMU-ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>異常電芯ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>氣溶膠故障</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障狀態位</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簇電壓採樣異常</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能使能位1狀態</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>簇電壓,U16,0.1,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>過流鎖定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>運行電流值,I16,0.1,0,A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>電流鎖定值,I16,0.1,0,A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>過壓鎖定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大電壓ID,U16,1,0,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大電壓,U16,0.0001,0,V</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模組高溫鎖定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大溫度ID,U16,1,0,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大溫度,I16,0.1,0,℃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>門限溫度,I16,0.1,0,℃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>模組低溫鎖定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小溫度ID,U16,1,0,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小溫度,I16,0.1,0,℃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>極柱高溫鎖定</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1713,9 +1848,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C687EFA9-03CD-4934-A871-27C7AD5CF9F9}">
-  <dimension ref="A1:H259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFB2DF3-AB59-41C8-8873-2DF7058DF6F0}">
+  <dimension ref="A1:H365"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="2.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="28.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1">
@@ -4095,13 +4237,13 @@
         <v>165</v>
       </c>
       <c r="F124" t="s">
-        <v>245</v>
+        <v>166</v>
       </c>
       <c r="G124" t="s">
         <v>167</v>
       </c>
       <c r="H124" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -4115,7 +4257,7 @@
         <v>52</v>
       </c>
       <c r="D125" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -4143,7 +4285,7 @@
         <v>54</v>
       </c>
       <c r="D127" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -4157,13 +4299,13 @@
         <v>55</v>
       </c>
       <c r="D128" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E128" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -4177,19 +4319,19 @@
         <v>56</v>
       </c>
       <c r="D129" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E129" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F129" t="s">
+        <v>176</v>
+      </c>
+      <c r="G129" t="s">
         <v>175</v>
       </c>
-      <c r="G129" t="s">
-        <v>174</v>
-      </c>
       <c r="H129" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -4203,7 +4345,7 @@
         <v>57</v>
       </c>
       <c r="D130" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -4217,7 +4359,7 @@
         <v>58</v>
       </c>
       <c r="D131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -4231,10 +4373,10 @@
         <v>59</v>
       </c>
       <c r="D132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -4248,13 +4390,13 @@
         <v>60</v>
       </c>
       <c r="D133" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G133" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -4271,7 +4413,7 @@
         <v>104</v>
       </c>
       <c r="E134" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4288,7 +4430,7 @@
         <v>105</v>
       </c>
       <c r="E135" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -4365,7 +4507,7 @@
         <v>66</v>
       </c>
       <c r="D139" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F139" t="s">
         <v>42</v>
@@ -4385,7 +4527,7 @@
         <v>67</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -4402,10 +4544,10 @@
         <v>115</v>
       </c>
       <c r="E141" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G141" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -4425,7 +4567,7 @@
         <v>118</v>
       </c>
       <c r="G142" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H142" t="s">
         <v>158</v>
@@ -4442,16 +4584,16 @@
         <v>70</v>
       </c>
       <c r="D143" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E143" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F143" t="s">
         <v>154</v>
       </c>
       <c r="G143" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -4465,16 +4607,16 @@
         <v>71</v>
       </c>
       <c r="D144" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E144" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G144" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H144" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4488,16 +4630,16 @@
         <v>72</v>
       </c>
       <c r="D145" t="s">
+        <v>197</v>
+      </c>
+      <c r="E145" t="s">
+        <v>194</v>
+      </c>
+      <c r="G145" t="s">
+        <v>195</v>
+      </c>
+      <c r="H145" t="s">
         <v>196</v>
-      </c>
-      <c r="E145" t="s">
-        <v>193</v>
-      </c>
-      <c r="G145" t="s">
-        <v>194</v>
-      </c>
-      <c r="H145" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -4511,16 +4653,16 @@
         <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E146" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G146" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H146" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -4534,16 +4676,16 @@
         <v>74</v>
       </c>
       <c r="D147" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G147" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H147" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -4560,7 +4702,7 @@
         <v>120</v>
       </c>
       <c r="G148" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -4577,7 +4719,7 @@
         <v>122</v>
       </c>
       <c r="G149" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -4594,7 +4736,7 @@
         <v>123</v>
       </c>
       <c r="G150" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -4611,7 +4753,7 @@
         <v>124</v>
       </c>
       <c r="G151" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -4625,13 +4767,13 @@
         <v>75</v>
       </c>
       <c r="D152" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E152" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -4645,7 +4787,7 @@
         <v>76</v>
       </c>
       <c r="D153" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -4659,7 +4801,7 @@
         <v>77</v>
       </c>
       <c r="D154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4673,13 +4815,13 @@
         <v>78</v>
       </c>
       <c r="D155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F155" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G155" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4693,10 +4835,10 @@
         <v>79</v>
       </c>
       <c r="D156" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G156" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4710,7 +4852,7 @@
         <v>80</v>
       </c>
       <c r="D157" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -4724,13 +4866,13 @@
         <v>81</v>
       </c>
       <c r="D158" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E158" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H158" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -4744,13 +4886,13 @@
         <v>82</v>
       </c>
       <c r="D159" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E159" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F159" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -4764,16 +4906,16 @@
         <v>83</v>
       </c>
       <c r="D160" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E160" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F160" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G160" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -4790,10 +4932,10 @@
         <v>96</v>
       </c>
       <c r="G161" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H161" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -4807,13 +4949,13 @@
         <v>85</v>
       </c>
       <c r="D162" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F162" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H162" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -4827,10 +4969,10 @@
         <v>86</v>
       </c>
       <c r="D163" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G163" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -4844,13 +4986,13 @@
         <v>87</v>
       </c>
       <c r="D164" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F164" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G164" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -4864,13 +5006,13 @@
         <v>88</v>
       </c>
       <c r="D165" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E165" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F165" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -4884,13 +5026,13 @@
         <v>89</v>
       </c>
       <c r="D166" t="s">
+        <v>234</v>
+      </c>
+      <c r="E166" t="s">
+        <v>232</v>
+      </c>
+      <c r="F166" t="s">
         <v>233</v>
-      </c>
-      <c r="E166" t="s">
-        <v>231</v>
-      </c>
-      <c r="F166" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -5940,7 +6082,7 @@
         <v>167</v>
       </c>
       <c r="H217" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -5954,7 +6096,7 @@
         <v>52</v>
       </c>
       <c r="D218" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -5982,7 +6124,7 @@
         <v>54</v>
       </c>
       <c r="D220" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -5996,13 +6138,13 @@
         <v>55</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E221" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G221" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -6016,19 +6158,19 @@
         <v>56</v>
       </c>
       <c r="D222" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E222" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F222" t="s">
+        <v>176</v>
+      </c>
+      <c r="G222" t="s">
         <v>175</v>
       </c>
-      <c r="G222" t="s">
-        <v>174</v>
-      </c>
       <c r="H222" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -6042,7 +6184,7 @@
         <v>57</v>
       </c>
       <c r="D223" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -6056,7 +6198,7 @@
         <v>58</v>
       </c>
       <c r="D224" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -6070,10 +6212,10 @@
         <v>59</v>
       </c>
       <c r="D225" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E225" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -6087,13 +6229,13 @@
         <v>60</v>
       </c>
       <c r="D226" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F226" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G226" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -6110,7 +6252,7 @@
         <v>104</v>
       </c>
       <c r="E227" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -6127,7 +6269,7 @@
         <v>105</v>
       </c>
       <c r="E228" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
@@ -6204,7 +6346,7 @@
         <v>66</v>
       </c>
       <c r="D232" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F232" t="s">
         <v>42</v>
@@ -6224,7 +6366,7 @@
         <v>67</v>
       </c>
       <c r="D233" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -6241,10 +6383,10 @@
         <v>115</v>
       </c>
       <c r="E234" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G234" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -6264,7 +6406,7 @@
         <v>118</v>
       </c>
       <c r="G235" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H235" t="s">
         <v>158</v>
@@ -6281,16 +6423,16 @@
         <v>70</v>
       </c>
       <c r="D236" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E236" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F236" t="s">
         <v>154</v>
       </c>
       <c r="G236" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -6304,16 +6446,16 @@
         <v>71</v>
       </c>
       <c r="D237" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E237" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G237" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H237" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -6327,16 +6469,16 @@
         <v>72</v>
       </c>
       <c r="D238" t="s">
+        <v>197</v>
+      </c>
+      <c r="E238" t="s">
+        <v>194</v>
+      </c>
+      <c r="G238" t="s">
+        <v>195</v>
+      </c>
+      <c r="H238" t="s">
         <v>196</v>
-      </c>
-      <c r="E238" t="s">
-        <v>193</v>
-      </c>
-      <c r="G238" t="s">
-        <v>194</v>
-      </c>
-      <c r="H238" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -6350,16 +6492,16 @@
         <v>73</v>
       </c>
       <c r="D239" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E239" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G239" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H239" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -6373,16 +6515,16 @@
         <v>74</v>
       </c>
       <c r="D240" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E240" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G240" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H240" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -6399,7 +6541,7 @@
         <v>120</v>
       </c>
       <c r="G241" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -6416,7 +6558,7 @@
         <v>122</v>
       </c>
       <c r="G242" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -6433,7 +6575,7 @@
         <v>123</v>
       </c>
       <c r="G243" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -6450,7 +6592,7 @@
         <v>124</v>
       </c>
       <c r="G244" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -6464,16 +6606,16 @@
         <v>75</v>
       </c>
       <c r="D245" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E245" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F245" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G245" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -6487,7 +6629,7 @@
         <v>76</v>
       </c>
       <c r="D246" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -6501,7 +6643,7 @@
         <v>77</v>
       </c>
       <c r="D247" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -6515,13 +6657,13 @@
         <v>78</v>
       </c>
       <c r="D248" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F248" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G248" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -6535,13 +6677,13 @@
         <v>79</v>
       </c>
       <c r="D249" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F249" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G249" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -6555,7 +6697,7 @@
         <v>80</v>
       </c>
       <c r="D250" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -6569,13 +6711,13 @@
         <v>81</v>
       </c>
       <c r="D251" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E251" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H251" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -6589,13 +6731,13 @@
         <v>82</v>
       </c>
       <c r="D252" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F252" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G252" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -6609,16 +6751,16 @@
         <v>83</v>
       </c>
       <c r="D253" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E253" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F253" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G253" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
@@ -6635,10 +6777,10 @@
         <v>96</v>
       </c>
       <c r="G254" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H254" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -6652,10 +6794,10 @@
         <v>85</v>
       </c>
       <c r="D255" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F255" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -6669,10 +6811,10 @@
         <v>86</v>
       </c>
       <c r="D256" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G256" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -6686,13 +6828,13 @@
         <v>87</v>
       </c>
       <c r="D257" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F257" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G257" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -6706,7 +6848,7 @@
         <v>89</v>
       </c>
       <c r="D258" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E258" t="s">
         <v>6</v>
@@ -6726,16 +6868,2124 @@
         <v>90</v>
       </c>
       <c r="D259" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E259" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F259" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G259" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>260</v>
+      </c>
+      <c r="B260">
+        <v>4</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260" t="s">
+        <v>0</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1</v>
+      </c>
+      <c r="F260" t="s">
+        <v>2</v>
+      </c>
+      <c r="G260" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>261</v>
+      </c>
+      <c r="B261">
+        <v>4</v>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+      <c r="D261" t="s">
+        <v>4</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1</v>
+      </c>
+      <c r="F261" t="s">
+        <v>2</v>
+      </c>
+      <c r="G261" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>262</v>
+      </c>
+      <c r="B262">
+        <v>4</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262" t="s">
+        <v>5</v>
+      </c>
+      <c r="E262" t="s">
+        <v>6</v>
+      </c>
+      <c r="F262" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>263</v>
+      </c>
+      <c r="B263">
+        <v>4</v>
+      </c>
+      <c r="C263">
+        <v>4</v>
+      </c>
+      <c r="D263" t="s">
+        <v>8</v>
+      </c>
+      <c r="E263" t="s">
+        <v>6</v>
+      </c>
+      <c r="F263" t="s">
+        <v>7</v>
+      </c>
+      <c r="G263" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>264</v>
+      </c>
+      <c r="B264">
+        <v>4</v>
+      </c>
+      <c r="C264">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>250</v>
+      </c>
+      <c r="F264" t="s">
+        <v>251</v>
+      </c>
+      <c r="G264" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>265</v>
+      </c>
+      <c r="B265">
+        <v>4</v>
+      </c>
+      <c r="C265">
+        <v>6</v>
+      </c>
+      <c r="D265" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>266</v>
+      </c>
+      <c r="B266">
+        <v>4</v>
+      </c>
+      <c r="C266">
+        <v>7</v>
+      </c>
+      <c r="D266" t="s">
+        <v>13</v>
+      </c>
+      <c r="E266" t="s">
+        <v>127</v>
+      </c>
+      <c r="G266" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>267</v>
+      </c>
+      <c r="B267">
+        <v>4</v>
+      </c>
+      <c r="C267">
+        <v>8</v>
+      </c>
+      <c r="D267" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267" t="s">
+        <v>129</v>
+      </c>
+      <c r="G267" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>268</v>
+      </c>
+      <c r="B268">
+        <v>4</v>
+      </c>
+      <c r="C268">
+        <v>9</v>
+      </c>
+      <c r="D268" t="s">
+        <v>18</v>
+      </c>
+      <c r="E268" t="s">
+        <v>19</v>
+      </c>
+      <c r="F268" t="s">
+        <v>20</v>
+      </c>
+      <c r="G268" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>269</v>
+      </c>
+      <c r="B269">
+        <v>4</v>
+      </c>
+      <c r="C269">
+        <v>10</v>
+      </c>
+      <c r="D269" t="s">
+        <v>22</v>
+      </c>
+      <c r="E269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>20</v>
+      </c>
+      <c r="G269" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>270</v>
+      </c>
+      <c r="B270">
+        <v>4</v>
+      </c>
+      <c r="C270">
+        <v>11</v>
+      </c>
+      <c r="D270" t="s">
+        <v>23</v>
+      </c>
+      <c r="E270" t="s">
+        <v>24</v>
+      </c>
+      <c r="F270" t="s">
+        <v>25</v>
+      </c>
+      <c r="G270" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>271</v>
+      </c>
+      <c r="B271">
+        <v>4</v>
+      </c>
+      <c r="C271">
+        <v>12</v>
+      </c>
+      <c r="D271" t="s">
+        <v>26</v>
+      </c>
+      <c r="E271" t="s">
+        <v>24</v>
+      </c>
+      <c r="F271" t="s">
+        <v>25</v>
+      </c>
+      <c r="G271" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>272</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272">
+        <v>13</v>
+      </c>
+      <c r="D272" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>273</v>
+      </c>
+      <c r="B273">
+        <v>4</v>
+      </c>
+      <c r="C273">
+        <v>14</v>
+      </c>
+      <c r="D273" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>274</v>
+      </c>
+      <c r="B274">
+        <v>4</v>
+      </c>
+      <c r="C274">
+        <v>15</v>
+      </c>
+      <c r="D274" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>275</v>
+      </c>
+      <c r="B275">
+        <v>4</v>
+      </c>
+      <c r="C275">
+        <v>16</v>
+      </c>
+      <c r="D275" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>276</v>
+      </c>
+      <c r="B276">
+        <v>4</v>
+      </c>
+      <c r="C276">
+        <v>17</v>
+      </c>
+      <c r="D276" t="s">
+        <v>35</v>
+      </c>
+      <c r="E276" t="s">
+        <v>134</v>
+      </c>
+      <c r="G276" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>277</v>
+      </c>
+      <c r="B277">
+        <v>4</v>
+      </c>
+      <c r="C277">
+        <v>18</v>
+      </c>
+      <c r="D277" t="s">
+        <v>38</v>
+      </c>
+      <c r="F277" t="s">
+        <v>136</v>
+      </c>
+      <c r="G277" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>278</v>
+      </c>
+      <c r="B278">
+        <v>4</v>
+      </c>
+      <c r="C278">
+        <v>19</v>
+      </c>
+      <c r="D278" t="s">
+        <v>40</v>
+      </c>
+      <c r="E278" t="s">
+        <v>41</v>
+      </c>
+      <c r="F278" t="s">
+        <v>42</v>
+      </c>
+      <c r="G278" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>279</v>
+      </c>
+      <c r="B279">
+        <v>4</v>
+      </c>
+      <c r="C279">
+        <v>20</v>
+      </c>
+      <c r="D279" t="s">
+        <v>43</v>
+      </c>
+      <c r="E279" t="s">
+        <v>41</v>
+      </c>
+      <c r="F279" t="s">
+        <v>42</v>
+      </c>
+      <c r="G279" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>280</v>
+      </c>
+      <c r="B280">
+        <v>4</v>
+      </c>
+      <c r="C280">
+        <v>21</v>
+      </c>
+      <c r="D280" t="s">
+        <v>44</v>
+      </c>
+      <c r="F280" t="s">
+        <v>137</v>
+      </c>
+      <c r="G280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>281</v>
+      </c>
+      <c r="B281">
+        <v>4</v>
+      </c>
+      <c r="C281">
+        <v>22</v>
+      </c>
+      <c r="D281" t="s">
+        <v>47</v>
+      </c>
+      <c r="F281" t="s">
+        <v>138</v>
+      </c>
+      <c r="G281" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>282</v>
+      </c>
+      <c r="B282">
+        <v>4</v>
+      </c>
+      <c r="C282">
+        <v>23</v>
+      </c>
+      <c r="D282" t="s">
+        <v>49</v>
+      </c>
+      <c r="F282" t="s">
+        <v>138</v>
+      </c>
+      <c r="G282" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>283</v>
+      </c>
+      <c r="B283">
+        <v>4</v>
+      </c>
+      <c r="C283">
+        <v>24</v>
+      </c>
+      <c r="D283" t="s">
+        <v>50</v>
+      </c>
+      <c r="F283" t="s">
+        <v>138</v>
+      </c>
+      <c r="G283" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>284</v>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
+      <c r="C284">
+        <v>25</v>
+      </c>
+      <c r="D284" t="s">
+        <v>51</v>
+      </c>
+      <c r="F284" t="s">
+        <v>138</v>
+      </c>
+      <c r="G284" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>285</v>
+      </c>
+      <c r="B285">
+        <v>4</v>
+      </c>
+      <c r="C285">
+        <v>26</v>
+      </c>
+      <c r="D285" t="s">
+        <v>52</v>
+      </c>
+      <c r="F285" t="s">
+        <v>53</v>
+      </c>
+      <c r="G285" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>286</v>
+      </c>
+      <c r="B286">
+        <v>4</v>
+      </c>
+      <c r="C286">
+        <v>27</v>
+      </c>
+      <c r="D286" t="s">
+        <v>54</v>
+      </c>
+      <c r="F286" t="s">
+        <v>53</v>
+      </c>
+      <c r="G286" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>287</v>
+      </c>
+      <c r="B287">
+        <v>4</v>
+      </c>
+      <c r="C287">
+        <v>28</v>
+      </c>
+      <c r="D287" t="s">
+        <v>55</v>
+      </c>
+      <c r="F287" t="s">
+        <v>53</v>
+      </c>
+      <c r="G287" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>288</v>
+      </c>
+      <c r="B288">
+        <v>4</v>
+      </c>
+      <c r="C288">
+        <v>29</v>
+      </c>
+      <c r="D288" t="s">
+        <v>56</v>
+      </c>
+      <c r="F288" t="s">
+        <v>53</v>
+      </c>
+      <c r="G288" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>289</v>
+      </c>
+      <c r="B289">
+        <v>4</v>
+      </c>
+      <c r="C289">
+        <v>30</v>
+      </c>
+      <c r="D289" t="s">
+        <v>57</v>
+      </c>
+      <c r="F289" t="s">
+        <v>53</v>
+      </c>
+      <c r="G289" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>290</v>
+      </c>
+      <c r="B290">
+        <v>4</v>
+      </c>
+      <c r="C290">
+        <v>31</v>
+      </c>
+      <c r="D290" t="s">
+        <v>58</v>
+      </c>
+      <c r="F290" t="s">
+        <v>141</v>
+      </c>
+      <c r="G290" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>291</v>
+      </c>
+      <c r="B291">
+        <v>4</v>
+      </c>
+      <c r="C291">
+        <v>32</v>
+      </c>
+      <c r="D291" t="s">
+        <v>60</v>
+      </c>
+      <c r="F291" t="s">
+        <v>141</v>
+      </c>
+      <c r="G291" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>292</v>
+      </c>
+      <c r="B292">
+        <v>4</v>
+      </c>
+      <c r="C292">
+        <v>33</v>
+      </c>
+      <c r="D292" t="s">
+        <v>61</v>
+      </c>
+      <c r="F292" t="s">
+        <v>143</v>
+      </c>
+      <c r="G292" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>293</v>
+      </c>
+      <c r="B293">
+        <v>4</v>
+      </c>
+      <c r="C293">
+        <v>34</v>
+      </c>
+      <c r="D293" t="s">
+        <v>63</v>
+      </c>
+      <c r="F293" t="s">
+        <v>143</v>
+      </c>
+      <c r="G293" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>294</v>
+      </c>
+      <c r="B294">
+        <v>4</v>
+      </c>
+      <c r="C294">
+        <v>35</v>
+      </c>
+      <c r="D294" t="s">
+        <v>64</v>
+      </c>
+      <c r="E294" t="s">
+        <v>145</v>
+      </c>
+      <c r="F294" t="s">
+        <v>146</v>
+      </c>
+      <c r="G294" t="s">
+        <v>147</v>
+      </c>
+      <c r="H294" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>295</v>
+      </c>
+      <c r="B295">
+        <v>4</v>
+      </c>
+      <c r="C295">
+        <v>36</v>
+      </c>
+      <c r="D295" t="s">
+        <v>66</v>
+      </c>
+      <c r="E295" t="s">
+        <v>145</v>
+      </c>
+      <c r="F295" t="s">
+        <v>149</v>
+      </c>
+      <c r="H295" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>296</v>
+      </c>
+      <c r="B296">
+        <v>4</v>
+      </c>
+      <c r="C296">
+        <v>37</v>
+      </c>
+      <c r="D296" t="s">
+        <v>68</v>
+      </c>
+      <c r="E296" t="s">
+        <v>145</v>
+      </c>
+      <c r="F296" t="s">
+        <v>146</v>
+      </c>
+      <c r="G296" t="s">
+        <v>147</v>
+      </c>
+      <c r="H296" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>297</v>
+      </c>
+      <c r="B297">
+        <v>4</v>
+      </c>
+      <c r="C297">
+        <v>38</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" t="s">
+        <v>145</v>
+      </c>
+      <c r="F297" t="s">
+        <v>149</v>
+      </c>
+      <c r="H297" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>298</v>
+      </c>
+      <c r="B298">
+        <v>4</v>
+      </c>
+      <c r="C298">
+        <v>39</v>
+      </c>
+      <c r="D298" t="s">
+        <v>70</v>
+      </c>
+      <c r="E298" t="s">
+        <v>6</v>
+      </c>
+      <c r="F298" t="s">
+        <v>53</v>
+      </c>
+      <c r="G298" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>299</v>
+      </c>
+      <c r="B299">
+        <v>4</v>
+      </c>
+      <c r="C299">
+        <v>40</v>
+      </c>
+      <c r="D299" t="s">
+        <v>71</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1</v>
+      </c>
+      <c r="F299" t="s">
+        <v>53</v>
+      </c>
+      <c r="G299" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>300</v>
+      </c>
+      <c r="B300">
+        <v>4</v>
+      </c>
+      <c r="C300">
+        <v>41</v>
+      </c>
+      <c r="D300" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>301</v>
+      </c>
+      <c r="B301">
+        <v>4</v>
+      </c>
+      <c r="C301">
+        <v>42</v>
+      </c>
+      <c r="D301" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>302</v>
+      </c>
+      <c r="B302">
+        <v>4</v>
+      </c>
+      <c r="C302">
+        <v>43</v>
+      </c>
+      <c r="D302" t="s">
+        <v>76</v>
+      </c>
+      <c r="E302" t="s">
+        <v>118</v>
+      </c>
+      <c r="G302" t="s">
+        <v>157</v>
+      </c>
+      <c r="H302" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>303</v>
+      </c>
+      <c r="B303">
+        <v>4</v>
+      </c>
+      <c r="C303">
+        <v>44</v>
+      </c>
+      <c r="D303" t="s">
+        <v>78</v>
+      </c>
+      <c r="E303" t="s">
+        <v>118</v>
+      </c>
+      <c r="G303" t="s">
+        <v>159</v>
+      </c>
+      <c r="H303" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>304</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304">
+        <v>45</v>
+      </c>
+      <c r="D304" t="s">
+        <v>80</v>
+      </c>
+      <c r="E304" t="s">
+        <v>118</v>
+      </c>
+      <c r="G304" t="s">
+        <v>160</v>
+      </c>
+      <c r="H304" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>305</v>
+      </c>
+      <c r="B305">
+        <v>4</v>
+      </c>
+      <c r="C305">
+        <v>46</v>
+      </c>
+      <c r="D305" t="s">
+        <v>82</v>
+      </c>
+      <c r="E305" t="s">
+        <v>118</v>
+      </c>
+      <c r="G305" t="s">
+        <v>159</v>
+      </c>
+      <c r="H305" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>306</v>
+      </c>
+      <c r="B306">
+        <v>4</v>
+      </c>
+      <c r="C306">
+        <v>47</v>
+      </c>
+      <c r="D306" t="s">
+        <v>83</v>
+      </c>
+      <c r="E306" t="s">
+        <v>118</v>
+      </c>
+      <c r="G306" t="s">
+        <v>160</v>
+      </c>
+      <c r="H306" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>307</v>
+      </c>
+      <c r="B307">
+        <v>4</v>
+      </c>
+      <c r="C307">
+        <v>48</v>
+      </c>
+      <c r="D307" t="s">
+        <v>84</v>
+      </c>
+      <c r="E307" t="s">
+        <v>161</v>
+      </c>
+      <c r="F307" t="s">
+        <v>162</v>
+      </c>
+      <c r="G307" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>308</v>
+      </c>
+      <c r="B308">
+        <v>4</v>
+      </c>
+      <c r="C308">
+        <v>49</v>
+      </c>
+      <c r="D308" t="s">
+        <v>86</v>
+      </c>
+      <c r="E308" t="s">
+        <v>161</v>
+      </c>
+      <c r="F308" t="s">
+        <v>162</v>
+      </c>
+      <c r="G308" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>309</v>
+      </c>
+      <c r="B309">
+        <v>4</v>
+      </c>
+      <c r="C309">
+        <v>50</v>
+      </c>
+      <c r="D309" t="s">
+        <v>87</v>
+      </c>
+      <c r="E309" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>310</v>
+      </c>
+      <c r="B310">
+        <v>4</v>
+      </c>
+      <c r="C310">
+        <v>51</v>
+      </c>
+      <c r="D310" t="s">
+        <v>88</v>
+      </c>
+      <c r="E310" t="s">
+        <v>165</v>
+      </c>
+      <c r="F310" t="s">
+        <v>166</v>
+      </c>
+      <c r="G310" t="s">
+        <v>167</v>
+      </c>
+      <c r="H310" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>311</v>
+      </c>
+      <c r="B311">
+        <v>4</v>
+      </c>
+      <c r="C311">
+        <v>52</v>
+      </c>
+      <c r="D311" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>312</v>
+      </c>
+      <c r="B312">
+        <v>4</v>
+      </c>
+      <c r="C312">
+        <v>53</v>
+      </c>
+      <c r="D312" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>313</v>
+      </c>
+      <c r="B313">
+        <v>4</v>
+      </c>
+      <c r="C313">
+        <v>54</v>
+      </c>
+      <c r="D313" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>314</v>
+      </c>
+      <c r="B314">
+        <v>4</v>
+      </c>
+      <c r="C314">
+        <v>55</v>
+      </c>
+      <c r="D314" t="s">
+        <v>171</v>
+      </c>
+      <c r="E314" t="s">
+        <v>172</v>
+      </c>
+      <c r="G314" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>315</v>
+      </c>
+      <c r="B315">
+        <v>4</v>
+      </c>
+      <c r="C315">
+        <v>56</v>
+      </c>
+      <c r="D315" t="s">
+        <v>174</v>
+      </c>
+      <c r="E315" t="s">
+        <v>175</v>
+      </c>
+      <c r="F315" t="s">
+        <v>176</v>
+      </c>
+      <c r="G315" t="s">
+        <v>175</v>
+      </c>
+      <c r="H315" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>316</v>
+      </c>
+      <c r="B316">
+        <v>4</v>
+      </c>
+      <c r="C316">
+        <v>57</v>
+      </c>
+      <c r="D316" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>317</v>
+      </c>
+      <c r="B317">
+        <v>4</v>
+      </c>
+      <c r="C317">
+        <v>58</v>
+      </c>
+      <c r="D317" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>318</v>
+      </c>
+      <c r="B318">
+        <v>4</v>
+      </c>
+      <c r="C318">
+        <v>59</v>
+      </c>
+      <c r="D318" t="s">
+        <v>180</v>
+      </c>
+      <c r="E318" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>319</v>
+      </c>
+      <c r="B319">
+        <v>4</v>
+      </c>
+      <c r="C319">
+        <v>60</v>
+      </c>
+      <c r="D319" t="s">
+        <v>182</v>
+      </c>
+      <c r="F319" t="s">
+        <v>183</v>
+      </c>
+      <c r="G319" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>320</v>
+      </c>
+      <c r="B320">
+        <v>4</v>
+      </c>
+      <c r="C320">
+        <v>61</v>
+      </c>
+      <c r="D320" t="s">
+        <v>104</v>
+      </c>
+      <c r="E320" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>321</v>
+      </c>
+      <c r="B321">
+        <v>4</v>
+      </c>
+      <c r="C321">
+        <v>62</v>
+      </c>
+      <c r="D321" t="s">
+        <v>105</v>
+      </c>
+      <c r="E321" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>322</v>
+      </c>
+      <c r="B322">
+        <v>4</v>
+      </c>
+      <c r="C322">
+        <v>63</v>
+      </c>
+      <c r="D322" t="s">
+        <v>106</v>
+      </c>
+      <c r="E322" t="s">
+        <v>41</v>
+      </c>
+      <c r="F322" t="s">
+        <v>42</v>
+      </c>
+      <c r="G322" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>323</v>
+      </c>
+      <c r="B323">
+        <v>4</v>
+      </c>
+      <c r="C323">
+        <v>64</v>
+      </c>
+      <c r="D323" t="s">
+        <v>108</v>
+      </c>
+      <c r="E323" t="s">
+        <v>41</v>
+      </c>
+      <c r="F323" t="s">
+        <v>42</v>
+      </c>
+      <c r="G323" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>324</v>
+      </c>
+      <c r="B324">
+        <v>4</v>
+      </c>
+      <c r="C324">
+        <v>65</v>
+      </c>
+      <c r="D324" t="s">
+        <v>109</v>
+      </c>
+      <c r="G324" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>325</v>
+      </c>
+      <c r="B325">
+        <v>4</v>
+      </c>
+      <c r="C325">
+        <v>66</v>
+      </c>
+      <c r="D325" t="s">
+        <v>185</v>
+      </c>
+      <c r="F325" t="s">
+        <v>42</v>
+      </c>
+      <c r="G325" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>326</v>
+      </c>
+      <c r="B326">
+        <v>4</v>
+      </c>
+      <c r="C326">
+        <v>67</v>
+      </c>
+      <c r="D326" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>327</v>
+      </c>
+      <c r="B327">
+        <v>4</v>
+      </c>
+      <c r="C327">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>115</v>
+      </c>
+      <c r="E327" t="s">
+        <v>187</v>
+      </c>
+      <c r="G327" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>328</v>
+      </c>
+      <c r="B328">
+        <v>4</v>
+      </c>
+      <c r="C328">
+        <v>69</v>
+      </c>
+      <c r="D328" t="s">
+        <v>117</v>
+      </c>
+      <c r="E328" t="s">
+        <v>118</v>
+      </c>
+      <c r="G328" t="s">
+        <v>189</v>
+      </c>
+      <c r="H328" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>329</v>
+      </c>
+      <c r="B329">
+        <v>4</v>
+      </c>
+      <c r="C329">
+        <v>70</v>
+      </c>
+      <c r="D329" t="s">
+        <v>190</v>
+      </c>
+      <c r="E329" t="s">
+        <v>191</v>
+      </c>
+      <c r="F329" t="s">
+        <v>154</v>
+      </c>
+      <c r="G329" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>330</v>
+      </c>
+      <c r="B330">
+        <v>4</v>
+      </c>
+      <c r="C330">
+        <v>71</v>
+      </c>
+      <c r="D330" t="s">
+        <v>193</v>
+      </c>
+      <c r="E330" t="s">
+        <v>194</v>
+      </c>
+      <c r="G330" t="s">
+        <v>195</v>
+      </c>
+      <c r="H330" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>331</v>
+      </c>
+      <c r="B331">
+        <v>4</v>
+      </c>
+      <c r="C331">
+        <v>72</v>
+      </c>
+      <c r="D331" t="s">
+        <v>197</v>
+      </c>
+      <c r="E331" t="s">
+        <v>194</v>
+      </c>
+      <c r="G331" t="s">
+        <v>195</v>
+      </c>
+      <c r="H331" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>332</v>
+      </c>
+      <c r="B332">
+        <v>4</v>
+      </c>
+      <c r="C332">
+        <v>73</v>
+      </c>
+      <c r="D332" t="s">
+        <v>198</v>
+      </c>
+      <c r="E332" t="s">
+        <v>194</v>
+      </c>
+      <c r="G332" t="s">
+        <v>195</v>
+      </c>
+      <c r="H332" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>333</v>
+      </c>
+      <c r="B333">
+        <v>4</v>
+      </c>
+      <c r="C333">
+        <v>74</v>
+      </c>
+      <c r="D333" t="s">
+        <v>199</v>
+      </c>
+      <c r="E333" t="s">
+        <v>194</v>
+      </c>
+      <c r="G333" t="s">
+        <v>195</v>
+      </c>
+      <c r="H333" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>334</v>
+      </c>
+      <c r="B334">
+        <v>4</v>
+      </c>
+      <c r="C334">
+        <v>128</v>
+      </c>
+      <c r="D334" t="s">
+        <v>120</v>
+      </c>
+      <c r="G334" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>335</v>
+      </c>
+      <c r="B335">
+        <v>4</v>
+      </c>
+      <c r="C335">
+        <v>129</v>
+      </c>
+      <c r="D335" t="s">
+        <v>122</v>
+      </c>
+      <c r="G335" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>336</v>
+      </c>
+      <c r="B336">
+        <v>4</v>
+      </c>
+      <c r="C336">
+        <v>130</v>
+      </c>
+      <c r="D336" t="s">
+        <v>123</v>
+      </c>
+      <c r="G336" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>337</v>
+      </c>
+      <c r="B337">
+        <v>4</v>
+      </c>
+      <c r="C337">
+        <v>131</v>
+      </c>
+      <c r="D337" t="s">
+        <v>124</v>
+      </c>
+      <c r="G337" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>338</v>
+      </c>
+      <c r="B338">
+        <v>4</v>
+      </c>
+      <c r="C338">
+        <v>75</v>
+      </c>
+      <c r="D338" t="s">
+        <v>201</v>
+      </c>
+      <c r="E338" t="s">
+        <v>202</v>
+      </c>
+      <c r="F338" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>339</v>
+      </c>
+      <c r="B339">
+        <v>4</v>
+      </c>
+      <c r="C339">
+        <v>76</v>
+      </c>
+      <c r="D339" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>340</v>
+      </c>
+      <c r="B340">
+        <v>4</v>
+      </c>
+      <c r="C340">
+        <v>77</v>
+      </c>
+      <c r="D340" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>341</v>
+      </c>
+      <c r="B341">
+        <v>4</v>
+      </c>
+      <c r="C341">
+        <v>78</v>
+      </c>
+      <c r="D341" t="s">
+        <v>206</v>
+      </c>
+      <c r="F341" t="s">
+        <v>207</v>
+      </c>
+      <c r="G341" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>342</v>
+      </c>
+      <c r="B342">
+        <v>4</v>
+      </c>
+      <c r="C342">
+        <v>79</v>
+      </c>
+      <c r="D342" t="s">
+        <v>209</v>
+      </c>
+      <c r="G342" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>343</v>
+      </c>
+      <c r="B343">
+        <v>4</v>
+      </c>
+      <c r="C343">
+        <v>80</v>
+      </c>
+      <c r="D343" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>344</v>
+      </c>
+      <c r="B344">
+        <v>4</v>
+      </c>
+      <c r="C344">
+        <v>81</v>
+      </c>
+      <c r="D344" t="s">
+        <v>212</v>
+      </c>
+      <c r="E344" t="s">
+        <v>213</v>
+      </c>
+      <c r="H344" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>345</v>
+      </c>
+      <c r="B345">
+        <v>4</v>
+      </c>
+      <c r="C345">
+        <v>82</v>
+      </c>
+      <c r="D345" t="s">
+        <v>215</v>
+      </c>
+      <c r="E345" t="s">
+        <v>216</v>
+      </c>
+      <c r="F345" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>346</v>
+      </c>
+      <c r="B346">
+        <v>4</v>
+      </c>
+      <c r="C346">
+        <v>83</v>
+      </c>
+      <c r="D346" t="s">
+        <v>218</v>
+      </c>
+      <c r="E346" t="s">
+        <v>219</v>
+      </c>
+      <c r="F346" t="s">
+        <v>220</v>
+      </c>
+      <c r="G346" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>347</v>
+      </c>
+      <c r="B347">
+        <v>4</v>
+      </c>
+      <c r="C347">
+        <v>84</v>
+      </c>
+      <c r="D347" t="s">
+        <v>96</v>
+      </c>
+      <c r="G347" t="s">
+        <v>222</v>
+      </c>
+      <c r="H347" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>348</v>
+      </c>
+      <c r="B348">
+        <v>4</v>
+      </c>
+      <c r="C348">
+        <v>85</v>
+      </c>
+      <c r="D348" t="s">
+        <v>224</v>
+      </c>
+      <c r="F348" t="s">
+        <v>222</v>
+      </c>
+      <c r="H348" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>349</v>
+      </c>
+      <c r="B349">
+        <v>4</v>
+      </c>
+      <c r="C349">
+        <v>86</v>
+      </c>
+      <c r="D349" t="s">
+        <v>226</v>
+      </c>
+      <c r="G349" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>350</v>
+      </c>
+      <c r="B350">
+        <v>4</v>
+      </c>
+      <c r="C350">
+        <v>87</v>
+      </c>
+      <c r="D350" t="s">
+        <v>228</v>
+      </c>
+      <c r="F350" t="s">
+        <v>229</v>
+      </c>
+      <c r="G350" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>351</v>
+      </c>
+      <c r="B351">
+        <v>4</v>
+      </c>
+      <c r="C351">
+        <v>88</v>
+      </c>
+      <c r="D351" t="s">
+        <v>231</v>
+      </c>
+      <c r="E351" t="s">
+        <v>232</v>
+      </c>
+      <c r="F351" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>352</v>
+      </c>
+      <c r="B352">
+        <v>4</v>
+      </c>
+      <c r="C352">
+        <v>89</v>
+      </c>
+      <c r="D352" t="s">
+        <v>234</v>
+      </c>
+      <c r="E352" t="s">
+        <v>232</v>
+      </c>
+      <c r="F352" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>353</v>
+      </c>
+      <c r="B353">
+        <v>4</v>
+      </c>
+      <c r="C353">
+        <v>90</v>
+      </c>
+      <c r="D353" t="s">
+        <v>253</v>
+      </c>
+      <c r="E353" t="s">
+        <v>254</v>
+      </c>
+      <c r="F353" t="s">
+        <v>255</v>
+      </c>
+      <c r="G353" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>354</v>
+      </c>
+      <c r="B354">
+        <v>4</v>
+      </c>
+      <c r="C354">
+        <v>91</v>
+      </c>
+      <c r="D354" t="s">
+        <v>246</v>
+      </c>
+      <c r="E354" t="s">
+        <v>257</v>
+      </c>
+      <c r="F354" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>355</v>
+      </c>
+      <c r="B355">
+        <v>4</v>
+      </c>
+      <c r="C355">
+        <v>92</v>
+      </c>
+      <c r="D355" t="s">
+        <v>259</v>
+      </c>
+      <c r="E355" t="s">
+        <v>260</v>
+      </c>
+      <c r="F355" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>356</v>
+      </c>
+      <c r="B356">
+        <v>4</v>
+      </c>
+      <c r="C356">
+        <v>93</v>
+      </c>
+      <c r="D356" t="s">
+        <v>262</v>
+      </c>
+      <c r="E356" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>357</v>
+      </c>
+      <c r="B357">
+        <v>4</v>
+      </c>
+      <c r="C357">
+        <v>94</v>
+      </c>
+      <c r="D357" t="s">
+        <v>264</v>
+      </c>
+      <c r="E357" t="s">
+        <v>265</v>
+      </c>
+      <c r="F357" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>358</v>
+      </c>
+      <c r="B358">
+        <v>4</v>
+      </c>
+      <c r="C358">
+        <v>95</v>
+      </c>
+      <c r="D358" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>359</v>
+      </c>
+      <c r="B359">
+        <v>4</v>
+      </c>
+      <c r="C359">
+        <v>96</v>
+      </c>
+      <c r="D359" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>360</v>
+      </c>
+      <c r="B360">
+        <v>4</v>
+      </c>
+      <c r="C360">
+        <v>97</v>
+      </c>
+      <c r="D360" t="s">
+        <v>267</v>
+      </c>
+      <c r="F360" t="s">
+        <v>268</v>
+      </c>
+      <c r="G360" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>361</v>
+      </c>
+      <c r="B361">
+        <v>4</v>
+      </c>
+      <c r="C361">
+        <v>98</v>
+      </c>
+      <c r="D361" t="s">
+        <v>270</v>
+      </c>
+      <c r="E361" t="s">
+        <v>271</v>
+      </c>
+      <c r="F361" t="s">
+        <v>272</v>
+      </c>
+      <c r="G361" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>362</v>
+      </c>
+      <c r="B362">
+        <v>4</v>
+      </c>
+      <c r="C362">
+        <v>99</v>
+      </c>
+      <c r="D362" t="s">
+        <v>273</v>
+      </c>
+      <c r="E362" t="s">
+        <v>274</v>
+      </c>
+      <c r="F362" t="s">
+        <v>275</v>
+      </c>
+      <c r="G362" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>363</v>
+      </c>
+      <c r="B363">
+        <v>4</v>
+      </c>
+      <c r="C363">
+        <v>100</v>
+      </c>
+      <c r="D363" t="s">
+        <v>277</v>
+      </c>
+      <c r="E363" t="s">
+        <v>278</v>
+      </c>
+      <c r="F363" t="s">
+        <v>279</v>
+      </c>
+      <c r="G363" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>364</v>
+      </c>
+      <c r="B364">
+        <v>4</v>
+      </c>
+      <c r="C364">
+        <v>101</v>
+      </c>
+      <c r="D364" t="s">
+        <v>280</v>
+      </c>
+      <c r="E364" t="s">
+        <v>274</v>
+      </c>
+      <c r="F364" t="s">
+        <v>275</v>
+      </c>
+      <c r="G364" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>365</v>
+      </c>
+      <c r="B365">
+        <v>4</v>
+      </c>
+      <c r="C365">
+        <v>102</v>
+      </c>
+      <c r="D365" t="s">
+        <v>249</v>
+      </c>
+      <c r="E365" t="s">
+        <v>274</v>
+      </c>
+      <c r="F365" t="s">
+        <v>275</v>
+      </c>
+      <c r="G365" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
